--- a/data/trans_camb/IP16A10-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 1,55</t>
+          <t>-17,18; 1,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 0,11</t>
+          <t>-17,83; 0,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 3,5</t>
+          <t>-7,04; 3,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 0,0</t>
+          <t>-10,72; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 1,14</t>
+          <t>-9,3; 1,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,08; -0,9</t>
+          <t>-11,49; -0,89</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,21</t>
+          <t>-100,0; 84,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-93,47; 74,96</t>
+          <t>-90,84; 127,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 1,44</t>
+          <t>-11,33; 1,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 1,18</t>
+          <t>-11,83; 0,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 1,76</t>
+          <t>-5,46; 1,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 2,89</t>
+          <t>-4,28; 2,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 1,03</t>
+          <t>-6,08; 0,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 1,2</t>
+          <t>-5,99; 1,2</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 120,1</t>
+          <t>-100,0; 173,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 114,35</t>
+          <t>-100,0; 104,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 113,32</t>
+          <t>-100,0; 121,25</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 0,0</t>
+          <t>-18,85; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 0,0</t>
+          <t>-18,85; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,17</t>
+          <t>0,0; 8,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,26</t>
+          <t>0,0; 9,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 0,95</t>
+          <t>-7,76; 0,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 2,41</t>
+          <t>-5,64; 2,42</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 12,09</t>
+          <t>-4,59; 11,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 0,0</t>
+          <t>-10,45; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 4,73</t>
+          <t>-2,83; 5,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 0,0</t>
+          <t>-5,63; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,41; -0,62</t>
+          <t>-7,56; -0,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,43; -1,65</t>
+          <t>-7,94; -1,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,8</t>
+          <t>-2,17; 3,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,79</t>
+          <t>-2,93; 1,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,28</t>
+          <t>-3,86; 0,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,32; -0,46</t>
+          <t>-4,49; -0,49</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-90,2; 0,29</t>
+          <t>-91,65; -6,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-95,53; -26,48</t>
+          <t>-95,06; -31,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-77,32; 420,35</t>
+          <t>-71,11; 662,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-76,16; 19,48</t>
+          <t>-77,19; 16,97</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-87,83; -7,41</t>
+          <t>-88,89; -7,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A10-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 1,44</t>
+          <t>-16,51; 2,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 0,11</t>
+          <t>-17,53; 0,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 3,5</t>
+          <t>-9,27; 3,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 0,0</t>
+          <t>-10,25; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 1,52</t>
+          <t>-9,77; 1,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,49; -0,89</t>
+          <t>-10,71; -0,74</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 84,76</t>
+          <t>-93,96; 132,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-90,84; 127,25</t>
+          <t>-92,16; 103,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 96,65</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 1,35</t>
+          <t>-12,0; 1,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 0,85</t>
+          <t>-11,99; 0,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 1,76</t>
+          <t>-5,73; 1,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 2,88</t>
+          <t>-4,31; 2,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 0,99</t>
+          <t>-6,2; 0,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 1,2</t>
+          <t>-6,04; 1,15</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 146,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 173,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 104,79</t>
+          <t>-100,0; 113,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 121,25</t>
+          <t>-100,0; 128,88</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 0,0</t>
+          <t>-17,02; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 0,0</t>
+          <t>-17,03; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,47</t>
+          <t>0,0; 10,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,96</t>
+          <t>0,0; 12,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 0,95</t>
+          <t>-7,25; 1,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 2,42</t>
+          <t>-6,35; 2,45</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 11,75</t>
+          <t>-4,81; 11,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 0,0</t>
+          <t>-10,75; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 5,42</t>
+          <t>-2,83; 4,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 0,0</t>
+          <t>-6,56; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,56; -0,71</t>
+          <t>-7,67; -0,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,94; -1,54</t>
+          <t>-8,47; -1,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,12</t>
+          <t>-2,55; 2,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,82</t>
+          <t>-2,94; 1,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,2</t>
+          <t>-3,74; 0,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -0,49</t>
+          <t>-4,26; -0,47</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-91,65; -6,11</t>
+          <t>-90,95; -11,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-95,06; -31,45</t>
+          <t>-100,0; -29,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-71,11; 662,14</t>
+          <t>-80,52; 446,25</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 320,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-77,19; 16,97</t>
+          <t>-76,9; 16,56</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-88,89; -7,86</t>
+          <t>-88,33; -8,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A10-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Edad-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea</t>
+          <t>Menores que consumieron  medicamentos para la diarrea</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,58</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,31</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-6,04</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-7,58</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,31</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 2,06</t>
+          <t>-7,4; 3,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,53; 0,18</t>
+          <t>-11,54; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 3,46</t>
+          <t>-16,14; 1,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 0,0</t>
+          <t>-18,16; 0,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 1,39</t>
+          <t>-10,02; 1,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,71; -0,74</t>
+          <t>-11,08; -0,9</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-24,89%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-63,36%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-79,46%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-24,89%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-93,96; 132,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 75,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-92,16; 103,45</t>
+          <t>-93,47; 74,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 96,65</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-4,15</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-4,34</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 1,3</t>
+          <t>-4,8; 1,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 0,89</t>
+          <t>-4,28; 2,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 1,76</t>
+          <t>-11,18; 1,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 2,87</t>
+          <t>-11,42; 1,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 0,85</t>
+          <t>-6,03; 1,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 1,15</t>
+          <t>-6,34; 1,2</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-38,61%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-1,68%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-63,02%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-65,87%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-38,61%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,68%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 146,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 120,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 113,16</t>
+          <t>-100,0; 114,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 128,88</t>
+          <t>-100,0; 113,32</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,01</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,27</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-5,25</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-5,25</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,01</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,27</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 0,0</t>
+          <t>0,0; 10,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 0,0</t>
+          <t>0,0; 11,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,14</t>
+          <t>-17,66; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,8</t>
+          <t>-17,66; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 1,31</t>
+          <t>-7,56; 0,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 2,45</t>
+          <t>-6,05; 2,41</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3,32</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,53</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,63; 12,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,68; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 11,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 4,81</t>
+          <t>-2,85; 4,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 0,0</t>
+          <t>-6,55; 0,0</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>76,27%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>76,27%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-3,66</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-4,34</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,67; -0,85</t>
+          <t>-2,52; 2,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,47; -1,57</t>
+          <t>-3,25; 1,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,59</t>
+          <t>-7,41; -0,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,81</t>
+          <t>-8,43; -1,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,29</t>
+          <t>-3,68; 0,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,26; -0,47</t>
+          <t>-4,32; -0,46</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>13,61%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-26,32%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-67,5%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-80,02%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>13,61%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-26,32%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-90,95; -11,08</t>
+          <t>-77,32; 420,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -29,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-80,52; 446,25</t>
+          <t>-90,2; 0,29</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 320,71</t>
+          <t>-95,53; -26,48</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-76,9; 16,56</t>
+          <t>-76,16; 19,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-88,33; -8,58</t>
+          <t>-87,83; -7,41</t>
         </is>
       </c>
     </row>
